--- a/inst/ext_data/scenario_parameters_2.xlsx
+++ b/inst/ext_data/scenario_parameters_2.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D8F39221-EDD6-44CA-8FC1-1870DAA1220B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Description" sheetId="7" r:id="rId1"/>
@@ -21,7 +21,6 @@
     <sheet name="HighPrice" sheetId="19" r:id="rId6"/>
   </sheets>
   <calcPr calcId="191029"/>
-  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
